--- a/travel_agent_forms/012_group_travel_arrangement_request_form--travel_agent_forms.xlsx
+++ b/travel_agent_forms/012_group_travel_arrangement_request_form--travel_agent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'leisure'}</t>
+          <t>leisure</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Leisure'}</t>
+          <t>Leisure</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'personal'}</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Personal'}</t>
+          <t>Personal</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'hotel'}</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Hotel'}</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'resort'}</t>
+          <t>resort</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Resort'}</t>
+          <t>Resort</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'hostel'}</t>
+          <t>hostel</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Hostel'}</t>
+          <t>Hostel</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'done'}</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Done'}</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
